--- a/FPSDemo/MiniTemplate/Datas/#enemy_wave_config.xlsx
+++ b/FPSDemo/MiniTemplate/Datas/#enemy_wave_config.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="enemy_wave_config" sheetId="1" r:id="Rd959e579582e4be4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="enemy_wave_config" sheetId="1" r:id="R3a4311adb6b44448"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -560,28 +560,28 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="F5" s="4" t="n">
-        <x:v>3</x:v>
+        <x:v>0.85</x:v>
       </x:c>
       <x:c r="G5" s="4" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H5" s="4" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="I5" s="4" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="J5" s="4" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="K5" s="4" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K5" s="4" t="n">
-        <x:v>8</x:v>
-      </x:c>
       <x:c r="L5" s="4" t="n">
-        <x:v>10</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="M5" s="4" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="N5" s="4" t="n">
         <x:v>1</x:v>
@@ -590,13 +590,13 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="P5" s="4" t="n">
-        <x:v>12</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="Q5" s="4" t="n">
-        <x:v>3</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="R5" s="4" t="n">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="S5" s="5" t="b">
         <x:v>1</x:v>
@@ -617,28 +617,28 @@
         <x:v>180</x:v>
       </x:c>
       <x:c r="F6" s="4" t="n">
-        <x:v>2.5</x:v>
+        <x:v>0.6</x:v>
       </x:c>
       <x:c r="G6" s="4" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H6" s="4" t="n">
-        <x:v>0.5</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I6" s="4" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="J6" s="4" t="n">
-        <x:v>16</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="K6" s="4" t="n">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="L6" s="4" t="n">
-        <x:v>14</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="M6" s="4" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="N6" s="4" t="n">
         <x:v>2</x:v>
@@ -647,13 +647,13 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="P6" s="4" t="n">
-        <x:v>20</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="Q6" s="4" t="n">
-        <x:v>4</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="R6" s="4" t="n">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="S6" s="5" t="b">
         <x:v>1</x:v>
@@ -674,28 +674,28 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F7" s="4" t="n">
-        <x:v>2</x:v>
+        <x:v>0.42</x:v>
       </x:c>
       <x:c r="G7" s="4" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="H7" s="4" t="n">
-        <x:v>0.5</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I7" s="4" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="J7" s="4" t="n">
-        <x:v>24</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K7" s="4" t="n">
-        <x:v>16</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="L7" s="4" t="n">
-        <x:v>18</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="M7" s="4" t="n">
-        <x:v>4</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="N7" s="4" t="n">
         <x:v>3</x:v>
@@ -704,13 +704,13 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="P7" s="4" t="n">
-        <x:v>30</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="Q7" s="4" t="n">
-        <x:v>6</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="R7" s="4" t="n">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="S7" s="5" t="b">
         <x:v>1</x:v>

--- a/FPSDemo/MiniTemplate/Datas/#enemy_wave_config.xlsx
+++ b/FPSDemo/MiniTemplate/Datas/#enemy_wave_config.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="enemy_wave_config" sheetId="1" r:id="R3a4311adb6b44448"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="enemy_wave_config" sheetId="1" r:id="R0061a88678c94946"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -674,28 +674,28 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F7" s="4" t="n">
-        <x:v>0.42</x:v>
+        <x:v>0.32</x:v>
       </x:c>
       <x:c r="G7" s="4" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H7" s="4" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I7" s="4" t="n">
-        <x:v>4</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="J7" s="4" t="n">
-        <x:v>30</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="K7" s="4" t="n">
-        <x:v>18</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="L7" s="4" t="n">
-        <x:v>30</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="M7" s="4" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="N7" s="4" t="n">
         <x:v>3</x:v>
@@ -704,10 +704,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="P7" s="4" t="n">
-        <x:v>100</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="Q7" s="4" t="n">
-        <x:v>15</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="R7" s="4" t="n">
         <x:v>2</x:v>
